--- a/pensum/ol13/OL13_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol13/OL13_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="171">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 13: Organisasjonens eksterne rammebetingelser (V5)</t>
   </si>
@@ -185,15 +185,42 @@
     <t xml:space="preserve">b)  Hvor mange kroner mer i rentekostnad i året gir renteøkningen på banklånet og kassekreditten til sammen? Regn på hele beløpet for et helt år.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rentekostnad = gjeld × rentesats. Endring = gjeld × endring i rentesats. Tilgangen på kapital og prisen på den bestemmer handlefriheten (Organisasjon og ledelse 13.6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Jobben er 1 800 000 kr med dekningsgrad 55,8 %. Med hvor mange prosent faller dekningsbidraget hvis Nordlys gir 5 % rabatt? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dekningsbidrag = pris − variable kostnader (bidragsmetoden, Markedsføring 7.4.1). Dekningsgrad = DB / salgsinntekt × 100 (fra Økonomistyring; ikke i kap. 13).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Nesten alt materiellet til Nordlys kommer fra Polarlys, og nå kommer et nytt prisark. Hva anbefaler læreboka en bedrift som er så avhengig av én leverandør?   A: Samle enda mer av innkjøpet hos Polarlys for å få bedre rabatt   B: Bringe flere leverandører på banen, selv om det koster litt   C: Godta prisarket: en grossist er for stor til å forhandle med   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Kari har tid til å gå grundig inn i én av de fire eksterne sakene denne uka. Hvilken bør det være, og hva gjør hun? Bruk tallene fra b og c og bokas begrep markedsmakt.</t>
   </si>
   <si>
+    <t xml:space="preserve">Markedsmakt og styrkeforhold (13.1), leverandørmakt (13.2), myndighetenes rammer (13.5) og prisen på kapital (13.6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekstern aktør?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver sak: kommer den fra noen utenfor Nordlys som Kari kan ringe? Da er det en ekstern aktør. Kommer den fra en ansatt eller en beslutning Kari tar selv, er den intern (kap. 12).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rente og rabatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renteøkning = gjeld × 0,25 %. Dekningsbidrag = pris × dekningsgrad. Rabatten trekkes rett fra dekningsbidraget, fordi de variable kostnadene er de samme.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, innledningen (figur 13.1 interessentmodellen) og avsnitt 13.1, 13.2, 13.5 og 13.6. Dekningsgraden på entreprenørjobber: MA05. Rentetallene: faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -281,15 +308,36 @@
     <t xml:space="preserve">b)  Hva er montørenes lønn per betalt time? Del årslønna på de betalte timene og svar med to desimaler.</t>
   </si>
   <si>
+    <t xml:space="preserve">Timelønn = årslønn / betalte timer. Lønnskostnad = lønn × (1 + sats for sosiale kostnader), 46,8 % etter tabell 2.4 i Økonomistyring (ikke i kap. 13).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mange prosent ligger Fjells timelønn over tariffens fagarbeidersats på 282,95 kr? Svar med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Prosent over = (egen sats − tariffsats) / tariffsats × 100. Tariffsatsen er referansen, fordi det er den vi måler mot.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona sier: «Vi er ikke med i NHO Elektro, så tariffen gjelder ikke oss.» Hvilket svar er riktig?   A: Riktig: en tariffavtale binder bare medlemmene   B: Feil: deler av LOK er allmenngjort, så minstelønna gjelder også Fjell   C: Feil: alle el-bedrifter må melde seg inn i NHO Elektro   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Fjell betaler om lag 10 % over tariffsatsen, og driftsmarginen var 3,0 % første år. Er det lurt? Bruk minst to eksterne arbeidsbetingelser i svaret.</t>
   </si>
   <si>
+    <t xml:space="preserve">Eksterne forhold: organisasjonene i arbeidslivet (13.7), tilgang på arbeidskraft (13.11.2), konkurrenter (13.4) og bank (13.6). Lønnskostnad med 46,8 % sosiale kostnader (Økonomistyring tabell 2.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utenfra eller innenfra?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør: kan Mona endre dette ved å bestemme det selv i morgen? Kravet i FEK og tariffsatsen kan hun ikke. Lønnsnivået over tariffen og egen kompetanse er hennes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosent over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Først lønn per time: 560 000 / 1 800. Så forskjellen mot 282,95, delt på 282,95, ganger 100.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.2, 13.5, 13.6 og 13.7, og kap. 12. Tariffsatsen: protokoll nye lønnssatser LOK per 1. mai 2026. Allmenngjøringsloven § 5 og forskrift om delvis allmenngjøring av LOK (Arbeidstilsynet). FEK § 7 (DSB). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -350,15 +398,36 @@
     <t xml:space="preserve">b)  Prognosesenteret venter boligstart på rundt 20 000 i 2026 og 24 000 i 2028. Hvor mange prosent økning er det?</t>
   </si>
   <si>
+    <t xml:space="preserve">Endring i prosent = (nytt − gammelt) / gammelt × 100. Etterspørselsforhold er et samfunnsøkonomisk forhold (Organisasjon og ledelse 13.11 og 13.11.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Nordlys hadde 96 antenneoppdrag i 2022 og 22 i 2026. Hvor mange prosent er endringen? Én desimal, med minus foran.</t>
   </si>
   <si>
+    <t xml:space="preserve">Endring i prosent = (nytt − gammelt) / gammelt × 100. Teknologisk utvikling gir nye produkter, men fører også til at eksisterende produkter forsvinner (Organisasjon og ledelse 13.12).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Ronny sier: «Strengere miljøkrav betyr bare mer papir og dyrere kabel for oss.» Hva sier læreboka om miljømessige forhold?   A: Strengere miljøkrav er en ren trussel som gir lavere aktivitet   B: Klimakrisen er en trussel, men gir også nye muligheter; vær i forkant av lovgivningen   C: Miljøkrav gjelder industrien, ikke installatører   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hvilken av prosessene presser hver av de tre avdelingene mest? Foreslå ett tiltak per avdeling som ligger innenfor Nordlys' egen kontroll.</t>
   </si>
   <si>
+    <t xml:space="preserve">De mer perifere arbeidsbetingelsene (Organisasjon og ledelse 13.9–13.14) og vellykket tilpasning (11.4): de fleste bedrifter er så små i forhold til omgivelsene at det beste de kan håpe på, er vellykket tilpasning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvor hører renta?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slå opp 13.11.1: tilgang på kapital og rentenivå. Hvilken overskrift står avsnittet under?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endring i prosent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(nytt − gammelt) / gammelt × 100. Faller tallet, blir svaret negativt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.9–13.14. Boligstart: Prognosesenteret via Logistikkinside 08.09.2026. Styringsrenten: Norges Bank. Elbiler: Elbilforeningen, årsberetning 2025. Antenneoppdragene: MA06. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -419,6 +488,9 @@
     <t xml:space="preserve">a)  Hva blir rentekostnaden på banklånet i år med 7,75 % rente på 400 000 kr? Regn forenklet for hele året.</t>
   </si>
   <si>
+    <t xml:space="preserve">Rentekostnad = lån × rentesats. Tilgangen på kapital og prisen på den bestemmer handlefriheten (Organisasjon og ledelse 13.6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvilket avsnitt i kapitlet forklarer best hvorfor innlegget i Facebook-gruppa kan koste Fjell salg?   A: 13.8 Massemediene   B: 13.13 Kulturelle forhold: omdømme og opinion   C: 13.12 Teknologiske forhold   (skriv bokstaven)</t>
   </si>
   <si>
@@ -447,6 +519,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Hvilken av de mer perifere arbeidsbetingelsene vil påvirke Fjell mest de neste to årene, og hva gjør Mona nå? Ett tiltak, begrunnet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknologiske forhold (13.12), kulturelle forhold og omdømme (13.13), miljømessige forhold og lovgivning (13.14), og vellykket tilpasning (Organisasjon og ledelse 11.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omdømme eller medier?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les 13.8 og 13.13 igjen. Hvilket av dem handler om hva som skjer med salget når bedriften bryter det folk forventer?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kan Mona gjøre noe?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les 11.4: hva er det beste de fleste bedrifter kan håpe på? Er det det samme som å gjøre ingenting?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.6, 13.11–13.14 og kap. 11.4. NEK 400: DSB, «Overgangsregler for NEK 400», og NHO Elektro 04.06.2026. Elbiler: Elbilforeningen, årsberetning 2025. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -460,7 +547,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,8 +614,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -545,6 +654,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFFBF6EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -597,7 +724,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -650,7 +777,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -683,8 +830,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -712,7 +859,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1015,7 +1162,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1295,33 +1442,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(ABS(F26-(9))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+      <c r="B26" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="11" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
@@ -1331,58 +1463,149 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="F28" s="12"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(ABS(F28-(9))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="11" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="43" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="32">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1403,12 +1626,18 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1425,7 +1654,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1436,7 +1665,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1446,7 +1675,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1457,7 +1686,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1481,10 +1710,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1494,10 +1723,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1507,10 +1736,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1520,10 +1749,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1533,10 +1762,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1546,10 +1775,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1559,10 +1788,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1572,10 +1801,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1600,7 +1829,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1609,7 +1838,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1623,7 +1852,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1637,7 +1866,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1651,7 +1880,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1665,7 +1894,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1679,7 +1908,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1693,7 +1922,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1705,94 +1934,170 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(ABS(F26-(10))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="11" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="33" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(ABS(F28-(10))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="11" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="32">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1813,12 +2118,18 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1835,7 +2146,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1846,7 +2157,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1856,7 +2167,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1867,7 +2178,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1891,10 +2202,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1904,10 +2215,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1917,10 +2228,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1930,10 +2241,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1943,10 +2254,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1956,10 +2267,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1969,10 +2280,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1997,7 +2308,7 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2011,7 +2322,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2023,94 +2334,170 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(-77.1))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="11" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(-77.1))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2124,12 +2511,18 @@
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2146,7 +2539,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2157,7 +2550,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2167,7 +2560,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2178,7 +2571,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2202,10 +2595,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2215,10 +2608,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2228,10 +2621,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2241,10 +2634,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2254,10 +2647,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2267,10 +2660,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2280,10 +2673,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2293,10 +2686,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2321,7 +2714,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2333,32 +2726,22 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2366,27 +2749,22 @@
       <c r="E21" s="7"/>
       <c r="F21" s="10"/>
       <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2394,13 +2772,13 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2408,13 +2786,13 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2422,13 +2800,13 @@
       <c r="E25" s="7"/>
       <c r="F25" s="10"/>
       <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2440,9 +2818,9 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -2450,70 +2828,148 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2527,8 +2983,7 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
@@ -2537,9 +2992,15 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol13/OL13_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol13/OL13_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Eksterne arbeidsbetingelser er forhold utenfor organisasjonen som påvirker mulighetene til å nå målene. Interessentmodellen (figur 13.1) viser aktørene bedriften må ta hensyn til: kunder, leverandører, distributører, konkurrenter, myndigheter, bank og finans, organisasjonene i arbeidslivet og mediene. Styrkeforholdet avgjøres av hvem som har flest å velge mellom (13.1 og 13.2). Tilgangen på kapital og prisen på den bestemmer handlefriheten (13.6).</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til høsten 2026. Kari Nordlund har seks saker på pulten samme uke. Polarlys sender nytt prisark på kabel fra 1. november. Banken hever renta på banklånet (2 800 000 kr) og kassekreditten (300 000 kr) fra 7,5 % til 7,75 %. Det lokale eltilsynet varsler virksomhetstilsyn i november. Ronny vil at montørene skal jobbe overtid i november. En totalentreprenør har Nordlys som én av fire likeverdige elektroentreprenører på lista, og ber om 5 % rabatt på en jobb til 1 800 000 kr uten mva; jobben har dekningsgrad 55,8 %. Og Kari vurderer selv å kjøpe et termograferingskamera. Gå fram slik: sorter sakene i ekstern aktør eller ikke, regn hva renteøkningen og rabatten koster, og avgjør hvem som har makten.</t>
+    <t xml:space="preserve">Casen er lagt til høsten 2026. Kari Nordlund har seks saker på pulten samme uke. Polarlys sender nytt prisark på kabel fra 1. november. Banken hever renta på banklånet (2 800 000 kr) og kassekreditten (300 000 kr) fra 7,5 % til 7,75 %. Det lokale eltilsynet varsler virksomhetstilsyn i november. Ronny vil at montørene skal jobbe overtid i november. En totalentreprenør har Nordlys som én av fire likeverdige elektroentreprenører på lista, og ber om 5 % rabatt på en jobb til 1 800 000 kr uten merverdiavgift; jobben har dekningsgrad 55,8 %. Og Kari vurderer selv å kjøpe et termograferingskamera. Gå fram slik: sorter sakene i ekstern aktør eller ikke, regn hva renteøkningen og rabatten koster, og avgjør hvem som har makten.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">c)  Jobben er 1 800 000 kr med dekningsgrad 55,8 %. Med hvor mange prosent faller dekningsbidraget hvis Nordlys gir 5 % rabatt? Én desimal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dekningsbidrag = pris − variable kostnader (bidragsmetoden, Markedsføring 7.4.1). Dekningsgrad = DB / salgsinntekt × 100 (fra Økonomistyring; ikke i kap. 13).</t>
+    <t xml:space="preserve">Dekningsbidrag = pris − variable kostnader (bidragsmetoden, Markedsføring 7.4.1). Dekningsgrad = dekningsbidrag / salgsinntekt × 100 (fra Økonomistyring; ikke i kap. 13).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Nesten alt materiellet til Nordlys kommer fra Polarlys, og nå kommer et nytt prisark. Hva anbefaler læreboka en bedrift som er så avhengig av én leverandør?   A: Samle enda mer av innkjøpet hos Polarlys for å få bedre rabatt   B: Bringe flere leverandører på banen, selv om det koster litt   C: Godta prisarket: en grossist er for stor til å forhandle med   (skriv bokstaven)</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">Renteøkning = gjeld × 0,25 %. Dekningsbidrag = pris × dekningsgrad. Rabatten trekkes rett fra dekningsbidraget, fordi de variable kostnadene er de samme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, innledningen (figur 13.1 interessentmodellen) og avsnitt 13.1, 13.2, 13.5 og 13.6. Dekningsgraden på entreprenørjobber: MA05. Rentetallene: faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, innledningen (figur 13.1 interessentmodellen) og avsnitt 13.1, 13.2, 13.5 og 13.6. Dekningsgraden på entreprenørjobber: Markedsføring kap. 5. Rentetallene: faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">A2 · Fjell Elektro: tariff, tilsyn og bank. Hva er eksternt, og hva bestemmer Mona selv?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Organisasjonene i arbeidslivet påvirker bedriften gjennom tarifforhandlingene: hovedoppgjør annethvert år, mellomoppgjør i året mellom, og Hovedavtalen NHO–LO som gjelder fire år av gangen (13.7). Myndighetene legger rammer på nær sagt alle områder (13.5); for el-bedrifter gjelder kvalifikasjonskravet til faglig ansvarlig i FEK § 7. Det som kommer utenfra, er eksternt. Det bedriften bestemmer selv innenfor rammen, er internt (kap. 12).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fjell Elektro AS er i sitt andre driftsår. Bedriften er ikke medlem av NHO Elektro og har ingen egen tariffavtale. De to montørene har 560 000 kr i årslønn hver og 1 800 betalte timer i året (1 400 fakturerbare og 400 ikke-fakturerbare). Tariffens sats for fagarbeidere i Landsoverenskomsten for elektrofagene (LOK) er 282,95 kr per time fra 1. mai 2026. Mona er faglig ansvarlig etter FEK § 7. Banken krever kausjon fra Mona, og grossisten gir 30 dagers kreditt. Driftsmarginen første år var 3,0 %. Gå fram slik: sorter fakta i eksternt og internt, regn montørenes lønn per time, og sammenlikn med tariffsatsen.</t>
+    <t xml:space="preserve">Kort oppsummert: Organisasjonene i arbeidslivet påvirker bedriften gjennom tarifforhandlingene: hovedoppgjør annethvert år, mellomoppgjør i året mellom, og Hovedavtalen mellom Næringslivets Hovedorganisasjon (NHO) og Landsorganisasjonen i Norge (LO) som gjelder fire år av gangen (13.7). Myndighetene legger rammer på nær sagt alle områder (13.5); for el-bedrifter gjelder kvalifikasjonskravet til faglig ansvarlig i forskrift om elektroforetak og kvalifikasjonskrav (FEK) § 7. Det som kommer utenfra, er eksternt. Det bedriften bestemmer selv innenfor rammen, er internt (kap. 12).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fjell Elektro AS er i sitt andre driftsår. Bedriften er ikke medlem av NHO Elektro, elektrobransjens forening i Næringslivets Hovedorganisasjon (NHO), og har ingen egen tariffavtale. De to montørene har 560 000 kr i årslønn hver og 1 800 betalte timer i året (1 400 fakturerbare og 400 ikke-fakturerbare). Tariffens sats for fagarbeidere i Landsoverenskomsten for elektrofagene (LOK) er 282,95 kr per time fra 1. mai 2026. Mona er faglig ansvarlig etter § 7 i forskrift om elektroforetak og kvalifikasjonskrav (FEK). Banken krever kausjon fra Mona, og grossisten gir 30 dagers kreditt. Driftsmarginen første år var 3,0 %. Gå fram slik: sorter fakta i eksternt og internt, regn montørenes lønn per time, og sammenlikn med tariffsatsen.</t>
   </si>
   <si>
     <t xml:space="preserve">Montørlønn</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">1 800 per montør i året</t>
   </si>
   <si>
-    <t xml:space="preserve">Tariffsats (LOK)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282,95 kr/t, fagarbeider fra 1.5.2026</t>
+    <t xml:space="preserve">Tariffsats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282,95 kr per time, fagarbeider fra 1.5.2026</t>
   </si>
   <si>
     <t xml:space="preserve">NHO Elektro</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">Faglig ansvarlig</t>
   </si>
   <si>
-    <t xml:space="preserve">Mona, installatørprøven 2023 (FEK § 7)</t>
+    <t xml:space="preserve">Mona, installatørprøven 2023</t>
   </si>
   <si>
     <t xml:space="preserve">Banken</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">a)  Sorter faktaene. Er dette en ekstern arbeidsbetingelse, altså noe som kommer utenfra og som Fjell må forholde seg til? Svar ja eller nei for hver.</t>
   </si>
   <si>
-    <t xml:space="preserve">      Kravet i FEK § 7 til faglig ansvarlig   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Kravet til faglig ansvarlig i forskrift om elektroforetak og kvalifikasjonskrav § 7   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      Mona har bestått installatørprøven   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">      Tariffens sats på 282,95 kr/t   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Tariffens sats på 282,95 kr per time   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      Fjell betaler 560 000 kr i året   (Ja eller Nei)</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">Prosent over = (egen sats − tariffsats) / tariffsats × 100. Tariffsatsen er referansen, fordi det er den vi måler mot.</t>
   </si>
   <si>
-    <t xml:space="preserve">d)  Mona sier: «Vi er ikke med i NHO Elektro, så tariffen gjelder ikke oss.» Hvilket svar er riktig?   A: Riktig: en tariffavtale binder bare medlemmene   B: Feil: deler av LOK er allmenngjort, så minstelønna gjelder også Fjell   C: Feil: alle el-bedrifter må melde seg inn i NHO Elektro   (skriv bokstaven)</t>
+    <t xml:space="preserve">d)  Mona sier: «Vi er ikke med i NHO Elektro, så tariffen gjelder ikke oss.» Hvilket svar er riktig? NHO Elektro er elektrobransjens forening i Næringslivets Hovedorganisasjon (NHO).   A: Riktig: en tariffavtale binder bare medlemmene   B: Feil: deler av Landsoverenskomsten for elektrofagene er allmenngjort, så minstelønna gjelder også Fjell   C: Feil: alle el-bedrifter må melde seg inn i NHO Elektro   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Fjell betaler om lag 10 % over tariffsatsen, og driftsmarginen var 3,0 % første år. Er det lurt? Bruk minst to eksterne arbeidsbetingelser i svaret.</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">Utenfra eller innenfra?</t>
   </si>
   <si>
-    <t xml:space="preserve">Spør: kan Mona endre dette ved å bestemme det selv i morgen? Kravet i FEK og tariffsatsen kan hun ikke. Lønnsnivået over tariffen og egen kompetanse er hennes.</t>
+    <t xml:space="preserve">Spør: kan Mona endre dette ved å bestemme det selv i morgen? Kravet i forskrift om elektroforetak og kvalifikasjonskrav og tariffsatsen kan hun ikke. Lønnsnivået over tariffen og egen kompetanse er hennes.</t>
   </si>
   <si>
     <t xml:space="preserve">Prosent over</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Først lønn per time: 560 000 / 1 800. Så forskjellen mot 282,95, delt på 282,95, ganger 100.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.2, 13.5, 13.6 og 13.7, og kap. 12. Tariffsatsen: protokoll nye lønnssatser LOK per 1. mai 2026. Allmenngjøringsloven § 5 og forskrift om delvis allmenngjøring av LOK (Arbeidstilsynet). FEK § 7 (DSB). Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.2, 13.5, 13.6 og 13.7, og kap. 12. Tariffsatsen: protokoll nye lønnssatser i Landsoverenskomsten for elektrofagene (LOK) per 1. mai 2026. Allmenngjøringsloven § 5 og forskrift om delvis allmenngjøring av LOK (Arbeidstilsynet). Forskrift om elektroforetak og kvalifikasjonskrav (FEK) § 7 (Direktoratet for samfunnssikkerhet og beredskap). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: hvilke prosesser presser hvilken avdeling?</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">(nytt − gammelt) / gammelt × 100. Faller tallet, blir svaret negativt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.9–13.14. Boligstart: Prognosesenteret via Logistikkinside 08.09.2026. Styringsrenten: Norges Bank. Elbiler: Elbilforeningen, årsberetning 2025. Antenneoppdragene: MA06. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.9–13.14. Boligstart: Prognosesenteret via Logistikkinside 08.09.2026. Styringsrenten: Norges Bank. Elbiler: Elbilforeningen, årsberetning 2025. Antenneoppdragene: Markedsføring kap. 6. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B2 · Fjell Elektro: rente, ny norm og omdømme. Hva kan Mona gjøre?</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">Kort oppsummert: Prosessene kan ikke forhandles, men bedriften kan tilpasse seg dem og i noen grad påvirke dem. Kapitlets mål er å kunne gjøre rede for hvordan de eksterne arbeidsbetingelsene påvirker virksomheten. Bedrifter lever av omdømmet sitt: handler de mot allment aksepterte normer, får de først problemer med anseelsen og så med salget (13.13). Teknologien og regelverket flytter seg, og bedriften bør være i forkant av lovgivningen (13.12 og 13.14).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS går inn i sitt andre driftsår. Banklånet er 400 000 kr etter første avdrag, og banken hever renta fra 7,5 % til 7,75 % (regn forenklet på 400 000 kr for hele året). NEK 400:2026 gjelder fra 1. juli 2026, og PVC-isolert kabel kan ikke lenger brukes i nye anlegg. Anlegg prosjektert etter NEK 400:2022 ut 2026 må være ferdige innen utgangen av 2027. En kunde ventet tre dager og skrev om det i borettslagets Facebook-gruppe, der 12 beboere vurderer elbillader. 95,9 % av nye personbiler i 2025 var elbiler. Gå fram slik: regn rentekostnaden, plasser Facebook-saken i kapitlet, sjekk påstandene om normen, og vurder hva Mona kan gjøre.</t>
+    <t xml:space="preserve">Fjell Elektro AS går inn i sitt andre driftsår. Banklånet er 400 000 kr etter første avdrag, og banken hever renta fra 7,5 % til 7,75 % (regn forenklet på 400 000 kr for hele året). NEK 400:2026, normen for elektriske lavspenningsinstallasjoner fra Norsk Elektroteknisk Komite (NEK), gjelder fra 1. juli 2026, og kabel isolert med polyvinylklorid (PVC) kan ikke lenger brukes i nye anlegg. Anlegg prosjektert etter NEK 400:2022 ut 2026 må være ferdige innen utgangen av 2027. En kunde ventet tre dager og skrev om det i borettslagets Facebook-gruppe, der 12 beboere vurderer elbillader. 95,9 % av nye personbiler i 2025 var elbiler. Gå fram slik: regn rentekostnaden, plasser Facebook-saken i kapitlet, sjekk påstandene om normen, og vurder hva Mona kan gjøre.</t>
   </si>
   <si>
     <t xml:space="preserve">Banklån</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">c)  Stemmer påstanden? Svar ja eller nei for hver.</t>
   </si>
   <si>
-    <t xml:space="preserve">      NEK 400:2026 gjelder fra 1. juli 2026   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Normen NEK 400:2026 gjelder fra 1. juli 2026   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      Anlegg prosjektert etter 2022-utgaven ut 2026 må være ferdige innen utgangen av 2027   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">      PVC-isolert kabel kan fortsatt brukes i nye anlegg   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Fjell kan forhandle om normen med DSB   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Kabel isolert med polyvinylklorid (PVC) kan fortsatt brukes i nye anlegg   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Fjell kan forhandle om normen med Direktoratet for samfunnssikkerhet og beredskap   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      At gamle kabeltyper forsvinner, er et eksempel på at eksisterende produkter forsvinner   (Ja eller Nei)</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">Les 11.4: hva er det beste de fleste bedrifter kan håpe på? Er det det samme som å gjøre ingenting?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.6, 13.11–13.14 og kap. 11.4. NEK 400: DSB, «Overgangsregler for NEK 400», og NHO Elektro 04.06.2026. Elbiler: Elbilforeningen, årsberetning 2025. Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 13, avsnitt 13.6, 13.11–13.14 og kap. 11.4. NEK 400, normen fra Norsk Elektroteknisk Komite (NEK): Direktoratet for samfunnssikkerhet og beredskap (DSB), «Overgangsregler for NEK 400», og NHO Elektro i Næringslivets Hovedorganisasjon (NHO) 04.06.2026. Elbiler: Elbilforeningen, årsberetning 2025. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>68</v>
       </c>
@@ -1684,7 +1684,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>69</v>
       </c>
@@ -1974,7 +1974,7 @@
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
         <v>97</v>
       </c>
@@ -2048,7 +2048,7 @@
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
     </row>
-    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
         <v>100</v>
       </c>
@@ -2074,7 +2074,7 @@
       <c r="F41" s="18"/>
       <c r="G41" s="18"/>
     </row>
-    <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
         <v>104</v>
       </c>
@@ -2569,7 +2569,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>137</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="F39" s="18"/>
       <c r="G39" s="18"/>
     </row>
-    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
         <v>170</v>
       </c>

--- a/pensum/ol13/OL13_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol13/OL13_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="171">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 13: Organisasjonens eksterne rammebetingelser (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 13: Organisasjonens eksterne rammebetingelser (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>
